--- a/data/employees/EMP039/AST-EMP039-06.xlsx
+++ b/data/employees/EMP039/AST-EMP039-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Data Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,184 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Experiment Data Log - Drew Kim (R&amp;D)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Drew Kim | Role: Director | Location: Fremont | Date: 2025-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Experiment ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Next Steps</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP-2026-041</t>
+          <t>EMP039</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low-temp deposition</t>
+          <t>Ast Emp039 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP disclosure</t>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP-2026-042</t>
+          <t>EMP039</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novel etchant blend</t>
+          <t>Ast Emp039 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP-2026-043</t>
+          <t>EMP039</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface treatment A</t>
+          <t>Ast Emp039 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.51</v>
+        <v>94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Redesign</t>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-2026-044</t>
+          <t>EMP039</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plasma optimisation</t>
+          <t>Ast Emp039 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>86</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start Q3</t>
+          <t>Section 1: Department KPI performance. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>82</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>98</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>72</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>92</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>69</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>78</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>99</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>72</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>84</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>69</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp039 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>73</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP039</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP039 contributes to ast emp039 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>